--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130057503</v>
+        <v>130057501</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540248</v>
+        <v>540154</v>
       </c>
       <c r="R2" t="n">
-        <v>6737813</v>
+        <v>6737897</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130057501</v>
+        <v>130057502</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540154</v>
+        <v>540158</v>
       </c>
       <c r="R3" t="n">
-        <v>6737897</v>
+        <v>6737847</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130057502</v>
+        <v>130057503</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540158</v>
+        <v>540248</v>
       </c>
       <c r="R4" t="n">
-        <v>6737847</v>
+        <v>6737813</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,11 +969,11 @@
         <v>130057504</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,7 +1066,7 @@
         <v>131258730</v>
       </c>
       <c r="B6" t="n">
-        <v>57090</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2968-2026 artfynd.xlsx
+++ b/artfynd/A 2968-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057504</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,8 +1204,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131258730</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>